--- a/diseases/d169/2005-2009.xlsx
+++ b/diseases/d169/2005-2009.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1217,6 +1232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1655,6 +1685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1803,6 +1838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1948,6 +1988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2096,6 +2141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2244,6 +2294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2389,6 +2444,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2537,6 +2597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2685,6 +2750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2830,6 +2900,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2978,6 +3053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3126,6 +3206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3271,6 +3356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3419,6 +3509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3567,6 +3662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3712,6 +3812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3860,6 +3965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4008,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4153,6 +4268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4301,6 +4421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4446,6 +4571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4594,6 +4724,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4739,6 +4874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4887,6 +5027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5035,6 +5180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5180,6 +5330,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5328,6 +5483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5476,6 +5636,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5621,6 +5786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5769,6 +5939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5914,6 +6089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6062,6 +6242,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6207,6 +6392,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6355,6 +6545,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6503,6 +6698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6648,6 +6848,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6796,6 +7001,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6944,6 +7154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7089,6 +7304,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7237,6 +7457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7385,6 +7610,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7530,6 +7760,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7678,6 +7913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7826,6 +8066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7971,6 +8216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8119,6 +8369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8267,6 +8522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8412,6 +8672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8560,6 +8825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8708,6 +8978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8853,6 +9128,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9001,6 +9281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9149,6 +9434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9294,6 +9584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9442,6 +9737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9590,6 +9890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9735,6 +10040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9883,6 +10193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10031,6 +10346,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10176,6 +10496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10324,6 +10649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10472,6 +10802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10617,6 +10952,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10765,6 +11105,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10913,6 +11258,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11058,6 +11408,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11206,6 +11561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11354,6 +11714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11499,6 +11864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11647,6 +12017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11795,6 +12170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11940,6 +12320,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12088,6 +12473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12236,6 +12626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12381,6 +12776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12529,6 +12929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12677,6 +13082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12822,6 +13232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12970,6 +13385,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13118,6 +13538,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13263,6 +13688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13411,6 +13841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13559,6 +13994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13704,6 +14144,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13852,6 +14297,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13997,6 +14447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14145,6 +14600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14293,6 +14753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14438,6 +14903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14586,6 +15056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14734,6 +15209,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14879,6 +15359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15027,6 +15512,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15175,6 +15665,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15320,6 +15815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15468,6 +15968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15616,6 +16121,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15761,6 +16271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15909,6 +16424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16057,6 +16577,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16202,6 +16727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16350,6 +16880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16498,6 +17033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16643,6 +17183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16791,6 +17336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16939,6 +17489,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17084,6 +17639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17232,6 +17792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17380,6 +17945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17525,6 +18095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17673,6 +18248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17821,6 +18401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17966,6 +18551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18114,6 +18704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18262,6 +18857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18407,6 +19007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18555,6 +19160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18703,6 +19313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18848,6 +19463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18996,6 +19616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19144,6 +19769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19289,6 +19919,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19437,6 +20072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19585,6 +20225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19730,6 +20375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19878,6 +20528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20026,6 +20681,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20171,6 +20831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20319,6 +20984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20467,6 +21137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20612,6 +21287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20760,6 +21440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20908,6 +21593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21053,6 +21743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21201,6 +21896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21349,6 +22049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21494,6 +22199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21642,6 +22352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21790,6 +22505,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21935,6 +22655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22083,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22231,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22376,6 +23111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22524,6 +23264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22672,6 +23417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22817,6 +23567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22965,6 +23720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23113,6 +23873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23258,6 +24023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23406,6 +24176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23554,6 +24329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23699,6 +24479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23847,6 +24632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23995,6 +24785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24140,6 +24935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24288,6 +25088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24436,6 +25241,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24581,6 +25391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24729,6 +25544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24877,6 +25697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25022,6 +25847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25170,6 +26000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25318,6 +26153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25463,6 +26303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25611,6 +26456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25759,6 +26609,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25904,6 +26759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26050,6 +26910,11 @@
       <c r="S174" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">

--- a/diseases/d169/2005-2009.xlsx
+++ b/diseases/d169/2005-2009.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1074,11 +1044,6 @@
       <c r="R4" t="n">
         <v>0.004381174155988157</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1091,22 +1056,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1227,11 +1182,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1244,22 +1194,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,11 +1317,6 @@
       <c r="R6" t="n">
         <v>0.00208979235906712</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1394,22 +1329,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,11 +1455,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1547,22 +1467,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1680,11 +1590,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1697,22 +1602,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1833,11 +1728,6 @@
       <c r="R9" t="n">
         <v>0.0144749515306248</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1850,22 +1740,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1983,11 +1863,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2000,22 +1875,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2136,11 +2001,6 @@
       <c r="R11" t="n">
         <v>0.004381174155988157</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2153,22 +2013,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2289,11 +2139,6 @@
       <c r="R12" t="n">
         <v>0.0144749515306248</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2306,22 +2151,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2439,11 +2274,6 @@
       <c r="R13" t="n">
         <v>0.004179584718134241</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2456,22 +2286,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2592,11 +2412,6 @@
       <c r="R14" t="n">
         <v>0.01314352246796447</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2609,22 +2424,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2745,11 +2550,6 @@
       <c r="R15" t="n">
         <v>0.0289499030612496</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2762,22 +2562,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2895,11 +2685,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2912,22 +2697,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3048,11 +2823,6 @@
       <c r="R17" t="n">
         <v>0.008762348311976314</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3065,22 +2835,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3201,11 +2961,6 @@
       <c r="R18" t="n">
         <v>0.0144749515306248</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3218,22 +2973,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3351,11 +3096,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3368,22 +3108,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3504,11 +3234,6 @@
       <c r="R20" t="n">
         <v>0.008762348311976314</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3521,22 +3246,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3657,11 +3372,6 @@
       <c r="R21" t="n">
         <v>0.0289499030612496</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3674,22 +3384,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3807,11 +3507,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3824,22 +3519,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3960,11 +3645,6 @@
       <c r="R23" t="n">
         <v>0.004381174155988157</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3977,22 +3657,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4113,11 +3783,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4130,22 +3795,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4263,11 +3918,6 @@
       <c r="R25" t="n">
         <v>0.00208979235906712</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4280,22 +3930,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4416,11 +4056,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4433,22 +4068,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4566,11 +4191,6 @@
       <c r="R27" t="n">
         <v>0.03343667774507392</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4583,22 +4203,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4719,11 +4329,6 @@
       <c r="R28" t="n">
         <v>0.0144749515306248</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4736,22 +4341,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4869,11 +4464,6 @@
       <c r="R29" t="n">
         <v>0.02925709302693968</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4886,22 +4476,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5022,11 +4602,6 @@
       <c r="R30" t="n">
         <v>0.004381174155988157</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5039,22 +4614,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5175,11 +4740,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5192,22 +4752,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5325,11 +4875,6 @@
       <c r="R32" t="n">
         <v>0.00208979235906712</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5342,22 +4887,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5478,11 +5013,6 @@
       <c r="R33" t="n">
         <v>0.01752469662395263</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5495,22 +5025,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5631,11 +5151,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5648,22 +5163,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5781,11 +5286,6 @@
       <c r="R35" t="n">
         <v>0.004166100988266854</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5798,22 +5298,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5934,11 +5424,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5951,22 +5436,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6084,11 +5559,6 @@
       <c r="R37" t="n">
         <v>0.002083050494133427</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6101,22 +5571,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6237,11 +5697,6 @@
       <c r="R38" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6254,22 +5709,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6387,11 +5832,6 @@
       <c r="R39" t="n">
         <v>0.002083050494133427</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6404,22 +5844,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6540,11 +5970,6 @@
       <c r="R40" t="n">
         <v>0.00436402344458131</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6557,22 +5982,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6693,11 +6108,6 @@
       <c r="R41" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6710,22 +6120,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6843,11 +6243,6 @@
       <c r="R42" t="n">
         <v>0.004166100988266854</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6860,22 +6255,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6996,11 +6381,6 @@
       <c r="R43" t="n">
         <v>0.00436402344458131</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7013,22 +6393,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7149,11 +6519,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7166,22 +6531,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7299,11 +6654,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7316,22 +6666,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7452,11 +6792,6 @@
       <c r="R46" t="n">
         <v>0.01309207033374393</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7469,22 +6804,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7605,11 +6930,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7622,22 +6942,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7755,11 +7065,6 @@
       <c r="R48" t="n">
         <v>0.008332201976533707</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7772,22 +7077,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7908,11 +7203,6 @@
       <c r="R49" t="n">
         <v>0.00872804688916262</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7925,22 +7215,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8061,11 +7341,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8078,22 +7353,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8211,11 +7476,6 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8228,22 +7488,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8364,11 +7614,6 @@
       <c r="R52" t="n">
         <v>0.03491218755665048</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8381,22 +7626,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8517,11 +7752,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8534,22 +7764,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8667,11 +7887,6 @@
       <c r="R54" t="n">
         <v>0.006249151482400281</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8684,22 +7899,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8820,11 +8025,6 @@
       <c r="R55" t="n">
         <v>0.02182011722290655</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8837,22 +8037,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8973,11 +8163,6 @@
       <c r="R56" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8990,22 +8175,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9123,11 +8298,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9140,22 +8310,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9276,11 +8436,6 @@
       <c r="R58" t="n">
         <v>0.00872804688916262</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9293,22 +8448,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9429,11 +8574,6 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9446,22 +8586,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9579,11 +8709,6 @@
       <c r="R60" t="n">
         <v>0.08748812075360393</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9596,22 +8721,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9732,11 +8847,6 @@
       <c r="R61" t="n">
         <v>0.00436402344458131</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9749,22 +8859,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9885,11 +8985,6 @@
       <c r="R62" t="n">
         <v>0.01442774513099671</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9902,22 +8997,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10035,11 +9120,6 @@
       <c r="R63" t="n">
         <v>0.03332880790613483</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10052,22 +9132,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10188,11 +9258,6 @@
       <c r="R64" t="n">
         <v>0.00872804688916262</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10205,22 +9270,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10341,11 +9396,6 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10358,22 +9408,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10491,11 +9531,6 @@
       <c r="R66" t="n">
         <v>0.004166100988266854</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10508,22 +9543,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10644,11 +9669,6 @@
       <c r="R67" t="n">
         <v>0.00872804688916262</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10661,22 +9681,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10797,11 +9807,6 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10814,22 +9819,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10947,11 +9942,6 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10964,22 +9954,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11100,11 +10080,6 @@
       <c r="R70" t="n">
         <v>0.02173258798090523</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11117,22 +10092,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11253,11 +10218,6 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11270,22 +10230,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11403,11 +10353,6 @@
       <c r="R72" t="n">
         <v>0.002075631077207799</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11420,22 +10365,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11556,11 +10491,6 @@
       <c r="R73" t="n">
         <v>0.008693035192362092</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11573,22 +10503,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11709,11 +10629,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11726,22 +10641,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11859,11 +10764,6 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11876,22 +10776,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12012,11 +10902,6 @@
       <c r="R76" t="n">
         <v>0.02173258798090523</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12029,22 +10914,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12165,11 +11040,6 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12182,22 +11052,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12315,11 +11175,6 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12332,22 +11187,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12468,11 +11313,6 @@
       <c r="R79" t="n">
         <v>0.02607910557708627</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12485,22 +11325,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12621,11 +11451,6 @@
       <c r="R80" t="n">
         <v>0.01434443425192699</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12638,22 +11463,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12771,11 +11586,6 @@
       <c r="R81" t="n">
         <v>0.002075631077207799</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12788,22 +11598,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12924,11 +11724,6 @@
       <c r="R82" t="n">
         <v>0.02607910557708627</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12941,22 +11736,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13077,11 +11862,6 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13094,22 +11874,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13227,11 +11997,6 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13244,22 +12009,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13380,11 +12135,6 @@
       <c r="R85" t="n">
         <v>0.03911865836562941</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13397,22 +12147,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13533,11 +12273,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13550,22 +12285,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13683,11 +12408,6 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13700,22 +12420,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13836,11 +12546,6 @@
       <c r="R88" t="n">
         <v>0.03042562317326732</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13853,22 +12558,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13989,11 +12684,6 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14006,22 +12696,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14139,11 +12819,6 @@
       <c r="R90" t="n">
         <v>0.004151262154415599</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14156,22 +12831,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14292,11 +12957,6 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14309,22 +12969,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14442,11 +13092,6 @@
       <c r="R92" t="n">
         <v>0.002075631077207799</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14459,22 +13104,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14595,11 +13230,6 @@
       <c r="R93" t="n">
         <v>0.01303955278854314</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14612,22 +13242,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14748,11 +13368,6 @@
       <c r="R94" t="n">
         <v>0.02868886850385399</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14765,22 +13380,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14898,11 +13503,6 @@
       <c r="R95" t="n">
         <v>0.04151262154415598</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14915,22 +13515,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15051,11 +13641,6 @@
       <c r="R96" t="n">
         <v>0.004346517596181046</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15068,22 +13653,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15204,11 +13779,6 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15221,22 +13791,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15354,11 +13914,6 @@
       <c r="R98" t="n">
         <v>0.06642019447064958</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15371,22 +13926,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15507,11 +14052,6 @@
       <c r="R99" t="n">
         <v>0.02173258798090523</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15524,22 +14064,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15660,11 +14190,6 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15677,22 +14202,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15810,11 +14325,6 @@
       <c r="R101" t="n">
         <v>0.008302524308831197</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15827,22 +14337,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15963,11 +14463,6 @@
       <c r="R102" t="n">
         <v>0.008693035192362092</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15980,22 +14475,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16116,11 +14601,6 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16133,22 +14613,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16266,11 +14736,6 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16283,22 +14748,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16419,11 +14874,6 @@
       <c r="R105" t="n">
         <v>0.004331584715899372</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16436,22 +14886,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16572,11 +15012,6 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16589,22 +15024,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16722,11 +15147,6 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16739,22 +15159,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16875,11 +15285,6 @@
       <c r="R108" t="n">
         <v>0.004331584715899372</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16892,22 +15297,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17028,11 +15423,6 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17045,22 +15435,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17178,11 +15558,6 @@
       <c r="R110" t="n">
         <v>0.002067974615115286</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17195,22 +15570,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17331,11 +15696,6 @@
       <c r="R111" t="n">
         <v>0.004331584715899372</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17348,22 +15708,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17484,11 +15834,6 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17501,22 +15846,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17634,11 +15969,6 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17651,22 +15981,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17787,11 +16107,6 @@
       <c r="R114" t="n">
         <v>0.008663169431798744</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17804,22 +16119,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17940,11 +16245,6 @@
       <c r="R115" t="n">
         <v>0.01424361727485844</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17957,22 +16257,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18090,11 +16380,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18107,22 +16392,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18243,11 +16518,6 @@
       <c r="R117" t="n">
         <v>0.02165792357949686</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18260,22 +16530,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18396,11 +16656,6 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18413,22 +16668,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18546,11 +16791,6 @@
       <c r="R119" t="n">
         <v>0.002067974615115286</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18563,22 +16803,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18699,11 +16929,6 @@
       <c r="R120" t="n">
         <v>0.01299475414769812</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18716,22 +16941,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18852,11 +17067,6 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18869,22 +17079,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19002,11 +17202,6 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19019,22 +17214,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19155,11 +17340,6 @@
       <c r="R123" t="n">
         <v>0.03898426244309434</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19172,22 +17352,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19308,11 +17478,6 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19325,22 +17490,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19458,11 +17613,6 @@
       <c r="R125" t="n">
         <v>0.002067974615115286</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19475,22 +17625,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19611,11 +17751,6 @@
       <c r="R126" t="n">
         <v>0.004331584715899372</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19628,22 +17763,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19764,11 +17889,6 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19781,22 +17901,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19914,11 +18024,6 @@
       <c r="R128" t="n">
         <v>0.004135949230230571</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19931,22 +18036,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20067,11 +18162,6 @@
       <c r="R129" t="n">
         <v>0.008663169431798744</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20084,22 +18174,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20220,11 +18300,6 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20237,22 +18312,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20370,11 +18435,6 @@
       <c r="R131" t="n">
         <v>0.101330756140649</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20387,22 +18447,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20523,11 +18573,6 @@
       <c r="R132" t="n">
         <v>0.01299475414769812</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20540,22 +18585,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20676,11 +18711,6 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20693,22 +18723,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20826,11 +18846,6 @@
       <c r="R134" t="n">
         <v>0.05997126383834328</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20843,22 +18858,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -20979,11 +18984,6 @@
       <c r="R135" t="n">
         <v>0.008663169431798744</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20996,22 +18996,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21132,11 +19122,6 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21149,22 +19134,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21282,11 +19257,6 @@
       <c r="R137" t="n">
         <v>0.008271898460461143</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21299,22 +19269,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21435,11 +19395,6 @@
       <c r="R138" t="n">
         <v>0.004331584715899372</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21452,22 +19407,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21588,11 +19533,6 @@
       <c r="R139" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21605,22 +19545,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21738,11 +19668,6 @@
       <c r="R140" t="n">
         <v>0.002059872819538363</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21755,22 +19680,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21891,11 +19806,6 @@
       <c r="R141" t="n">
         <v>0.008633952820887223</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21908,22 +19818,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22044,11 +19944,6 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22061,22 +19956,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22194,11 +20079,6 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22211,22 +20091,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22347,11 +20217,6 @@
       <c r="R144" t="n">
         <v>0.01295092923133083</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22364,22 +20229,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22500,11 +20355,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22517,22 +20367,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22650,11 +20490,6 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22667,22 +20502,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22803,11 +20628,6 @@
       <c r="R147" t="n">
         <v>0.03885278769399251</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22820,22 +20640,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -22956,11 +20766,6 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22973,22 +20778,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23106,11 +20901,6 @@
       <c r="R149" t="n">
         <v>0.004119745639076727</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23123,22 +20913,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23259,11 +21039,6 @@
       <c r="R150" t="n">
         <v>0.01295092923133083</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23276,22 +21051,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23412,11 +21177,6 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23429,22 +21189,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23562,11 +21312,6 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23579,22 +21324,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23715,11 +21450,6 @@
       <c r="R153" t="n">
         <v>0.01726790564177445</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23732,22 +21462,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -23868,11 +21588,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23885,22 +21600,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24018,11 +21723,6 @@
       <c r="R155" t="n">
         <v>0.00617961845861509</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24035,22 +21735,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24171,11 +21861,6 @@
       <c r="R156" t="n">
         <v>0.008633952820887223</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24188,22 +21873,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24324,11 +21999,6 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24341,22 +22011,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24474,11 +22134,6 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24491,22 +22146,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -24627,11 +22272,6 @@
       <c r="R159" t="n">
         <v>0.03021883487310528</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24644,22 +22284,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24780,11 +22410,6 @@
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24797,22 +22422,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -24930,11 +22545,6 @@
       <c r="R161" t="n">
         <v>0.002059872819538363</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24947,22 +22557,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -25083,11 +22683,6 @@
       <c r="R162" t="n">
         <v>0.02158488205221806</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25100,22 +22695,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25236,11 +22821,6 @@
       <c r="R163" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25253,22 +22833,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25386,11 +22956,6 @@
       <c r="R164" t="n">
         <v>0.00617961845861509</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25403,22 +22968,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25539,11 +23094,6 @@
       <c r="R165" t="n">
         <v>0.01726790564177445</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25556,22 +23106,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -25692,11 +23232,6 @@
       <c r="R166" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25709,22 +23244,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -25842,11 +23367,6 @@
       <c r="R167" t="n">
         <v>0.01235923691723018</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25859,22 +23379,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -25995,11 +23505,6 @@
       <c r="R168" t="n">
         <v>0.008633952820887223</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26012,22 +23517,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26148,11 +23643,6 @@
       <c r="R169" t="n">
         <v>0.02831070116901255</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26165,22 +23655,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26298,11 +23778,6 @@
       <c r="R170" t="n">
         <v>0.01235923691723018</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26315,22 +23790,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26451,11 +23916,6 @@
       <c r="R171" t="n">
         <v>0.008633952820887223</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26468,22 +23928,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -26604,11 +24054,6 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26621,22 +24066,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -26754,11 +24189,6 @@
       <c r="R173" t="n">
         <v>0.01441910973676854</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26771,22 +24201,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -26907,11 +24327,6 @@
       <c r="R174" t="n">
         <v>0.004316976410443612</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26924,22 +24339,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>

--- a/diseases/d169/2005-2009.xlsx
+++ b/diseases/d169/2005-2009.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1182,6 +1212,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1194,12 +1229,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1317,6 +1362,11 @@
       <c r="R6" t="n">
         <v>0.00208979235906712</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1329,12 +1379,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1455,6 +1515,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1467,12 +1532,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1590,6 +1665,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1602,12 +1682,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1728,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0.0144749515306248</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1740,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1863,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1875,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2139,6 +2259,11 @@
       <c r="R12" t="n">
         <v>0.0144749515306248</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2151,12 +2276,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2274,6 +2409,11 @@
       <c r="R13" t="n">
         <v>0.004179584718134241</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2286,12 +2426,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2550,6 +2700,11 @@
       <c r="R15" t="n">
         <v>0.0289499030612496</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2562,12 +2717,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2685,6 +2850,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2697,12 +2867,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2961,6 +3141,11 @@
       <c r="R18" t="n">
         <v>0.0144749515306248</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2973,12 +3158,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3096,6 +3291,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3108,12 +3308,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3372,6 +3582,11 @@
       <c r="R21" t="n">
         <v>0.0289499030612496</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3384,12 +3599,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3507,6 +3732,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3519,12 +3749,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3783,6 +4023,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3795,12 +4040,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3918,6 +4173,11 @@
       <c r="R25" t="n">
         <v>0.00208979235906712</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3930,12 +4190,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4056,6 +4326,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4068,12 +4343,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4191,6 +4476,11 @@
       <c r="R27" t="n">
         <v>0.03343667774507392</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4203,12 +4493,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4329,6 +4629,11 @@
       <c r="R28" t="n">
         <v>0.0144749515306248</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4341,12 +4646,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4464,6 +4779,11 @@
       <c r="R29" t="n">
         <v>0.02925709302693968</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4476,12 +4796,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4740,6 +5070,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4752,12 +5087,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4875,6 +5220,11 @@
       <c r="R32" t="n">
         <v>0.00208979235906712</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4887,12 +5237,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5151,6 +5511,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5163,12 +5528,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5286,6 +5661,11 @@
       <c r="R35" t="n">
         <v>0.004166100988266854</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5298,12 +5678,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5424,6 +5814,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5436,12 +5831,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5559,6 +5964,11 @@
       <c r="R37" t="n">
         <v>0.002083050494133427</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5571,12 +5981,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5697,6 +6117,11 @@
       <c r="R38" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5709,12 +6134,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5832,6 +6267,11 @@
       <c r="R39" t="n">
         <v>0.002083050494133427</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5844,12 +6284,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6108,6 +6558,11 @@
       <c r="R41" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6120,12 +6575,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6243,6 +6708,11 @@
       <c r="R42" t="n">
         <v>0.004166100988266854</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6255,12 +6725,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6519,6 +6999,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6531,12 +7016,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6654,6 +7149,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6666,12 +7166,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6930,6 +7440,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6942,12 +7457,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7065,6 +7590,11 @@
       <c r="R48" t="n">
         <v>0.008332201976533707</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7077,12 +7607,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7341,6 +7881,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7353,12 +7898,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7476,6 +8031,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7488,12 +8048,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7752,6 +8322,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7764,12 +8339,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7887,6 +8472,11 @@
       <c r="R54" t="n">
         <v>0.006249151482400281</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7899,12 +8489,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8163,6 +8763,11 @@
       <c r="R56" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8175,12 +8780,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8298,6 +8913,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8310,12 +8930,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8574,6 +9204,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8586,12 +9221,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8709,6 +9354,11 @@
       <c r="R60" t="n">
         <v>0.08748812075360393</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8721,12 +9371,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8985,6 +9645,11 @@
       <c r="R62" t="n">
         <v>0.01442774513099671</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8997,12 +9662,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9120,6 +9795,11 @@
       <c r="R63" t="n">
         <v>0.03332880790613483</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9132,12 +9812,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9396,6 +10086,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9408,12 +10103,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9531,6 +10236,11 @@
       <c r="R66" t="n">
         <v>0.004166100988266854</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9543,12 +10253,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9807,6 +10527,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9819,12 +10544,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -9942,6 +10677,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9954,12 +10694,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10218,6 +10968,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10230,12 +10985,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10353,6 +11118,11 @@
       <c r="R72" t="n">
         <v>0.002075631077207799</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10365,12 +11135,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10629,6 +11409,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10641,12 +11426,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10764,6 +11559,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10776,12 +11576,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11040,6 +11850,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11052,12 +11867,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11175,6 +12000,11 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11187,12 +12017,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11451,6 +12291,11 @@
       <c r="R80" t="n">
         <v>0.01434443425192699</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11463,12 +12308,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11586,6 +12441,11 @@
       <c r="R81" t="n">
         <v>0.002075631077207799</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11598,12 +12458,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11862,6 +12732,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11874,12 +12749,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -11997,6 +12882,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12009,12 +12899,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12273,6 +13173,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12285,12 +13190,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12408,6 +13323,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12420,12 +13340,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12684,6 +13614,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12696,12 +13631,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -12819,6 +13764,11 @@
       <c r="R90" t="n">
         <v>0.004151262154415599</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12831,12 +13781,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -12957,6 +13917,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12969,12 +13934,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13092,6 +14067,11 @@
       <c r="R92" t="n">
         <v>0.002075631077207799</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13104,12 +14084,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13368,6 +14358,11 @@
       <c r="R94" t="n">
         <v>0.02868886850385399</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13380,12 +14375,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13503,6 +14508,11 @@
       <c r="R95" t="n">
         <v>0.04151262154415598</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13515,12 +14525,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13779,6 +14799,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13791,12 +14816,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -13914,6 +14949,11 @@
       <c r="R98" t="n">
         <v>0.06642019447064958</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13926,12 +14966,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14190,6 +15240,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14202,12 +15257,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14325,6 +15390,11 @@
       <c r="R101" t="n">
         <v>0.008302524308831197</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14337,12 +15407,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14601,6 +15681,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14613,12 +15698,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -14736,6 +15831,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14748,12 +15848,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15012,6 +16122,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15024,12 +16139,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15147,6 +16272,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15159,12 +16289,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15423,6 +16563,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15435,12 +16580,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15558,6 +16713,11 @@
       <c r="R110" t="n">
         <v>0.002067974615115286</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15570,12 +16730,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -15834,6 +17004,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15846,12 +17021,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -15969,6 +17154,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15981,12 +17171,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16245,6 +17445,11 @@
       <c r="R115" t="n">
         <v>0.01424361727485844</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16257,12 +17462,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16380,6 +17595,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16392,12 +17612,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -16656,6 +17886,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16668,12 +17903,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -16791,6 +18036,11 @@
       <c r="R119" t="n">
         <v>0.002067974615115286</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16803,12 +18053,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17067,6 +18327,11 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17079,12 +18344,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17202,6 +18477,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17214,12 +18494,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17478,6 +18768,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17490,12 +18785,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -17613,6 +18918,11 @@
       <c r="R125" t="n">
         <v>0.002067974615115286</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17625,12 +18935,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -17889,6 +19209,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17901,12 +19226,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18024,6 +19359,11 @@
       <c r="R128" t="n">
         <v>0.004135949230230571</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18036,12 +19376,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -18300,6 +19650,11 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18312,12 +19667,22 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -18435,6 +19800,11 @@
       <c r="R131" t="n">
         <v>0.101330756140649</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18447,12 +19817,22 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -18711,6 +20091,11 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18723,12 +20108,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -18846,6 +20241,11 @@
       <c r="R134" t="n">
         <v>0.05997126383834328</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18858,12 +20258,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19122,6 +20532,11 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19134,12 +20549,22 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -19257,6 +20682,11 @@
       <c r="R137" t="n">
         <v>0.008271898460461143</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19269,12 +20699,22 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19533,6 +20973,11 @@
       <c r="R139" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19545,12 +20990,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -19668,6 +21123,11 @@
       <c r="R140" t="n">
         <v>0.002059872819538363</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19680,12 +21140,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -19944,6 +21414,11 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19956,12 +21431,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -20079,6 +21564,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20091,12 +21581,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -20355,6 +21855,11 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20367,12 +21872,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -20490,6 +22005,11 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20502,12 +22022,22 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -20766,6 +22296,11 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20778,12 +22313,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -20901,6 +22446,11 @@
       <c r="R149" t="n">
         <v>0.004119745639076727</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20913,12 +22463,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21177,6 +22737,11 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21189,12 +22754,22 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -21312,6 +22887,11 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21324,12 +22904,22 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -21588,6 +23178,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21600,12 +23195,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -21723,6 +23328,11 @@
       <c r="R155" t="n">
         <v>0.00617961845861509</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21735,12 +23345,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -21999,6 +23619,11 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22011,12 +23636,22 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -22134,6 +23769,11 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22146,12 +23786,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22410,6 +24060,11 @@
       <c r="R160" t="n">
         <v>0</v>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22422,12 +24077,22 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -22545,6 +24210,11 @@
       <c r="R161" t="n">
         <v>0.002059872819538363</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22557,12 +24227,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -22821,6 +24501,11 @@
       <c r="R163" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22833,12 +24518,22 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -22956,6 +24651,11 @@
       <c r="R164" t="n">
         <v>0.00617961845861509</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22968,12 +24668,22 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23232,6 +24942,11 @@
       <c r="R166" t="n">
         <v>0.01415535058450628</v>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23244,12 +24959,22 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -23367,6 +25092,11 @@
       <c r="R167" t="n">
         <v>0.01235923691723018</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23379,12 +25109,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -23643,6 +25383,11 @@
       <c r="R169" t="n">
         <v>0.02831070116901255</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23655,12 +25400,22 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -23778,6 +25533,11 @@
       <c r="R170" t="n">
         <v>0.01235923691723018</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23790,12 +25550,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -24054,6 +25824,11 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24066,12 +25841,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -24189,6 +25974,11 @@
       <c r="R173" t="n">
         <v>0.01441910973676854</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24201,12 +25991,22 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
